--- a/revision/data/Supplementary/sfig12_source_data_market_readiness.xlsx
+++ b/revision/data/Supplementary/sfig12_source_data_market_readiness.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/79f001dfc2d9feea/Nature_Energy_SMRs_2026/Extended Data/Extended_Data_Files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/79f001dfc2d9feea/Nat. Comms v2/Supplementary source data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{3E28C4EF-F823-4FC7-9EFF-E5BF7046F7F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56C23D5D-9196-474F-9041-3DCF16F5558E}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="8_{3E28C4EF-F823-4FC7-9EFF-E5BF7046F7F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A43B2BD-00D8-4B21-A996-7BA2651719AC}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DADBFC90-5043-4ACD-BEBB-0FC40FCF19A7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{DADBFC90-5043-4ACD-BEBB-0FC40FCF19A7}"/>
   </bookViews>
   <sheets>
     <sheet name="NEA_market_readiness" sheetId="2" r:id="rId1"/>
@@ -445,7 +445,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -457,6 +457,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -482,13 +489,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -506,10 +517,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3107,11 +3114,11 @@
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="2">
-        <v>1</v>
+      <c r="B7" s="5">
+        <v>3</v>
       </c>
       <c r="C7" t="s">
         <v>19</v>
@@ -5561,11 +5568,11 @@
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
+      <c r="A55" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B55" s="2">
-        <v>4</v>
+      <c r="B55" s="5">
+        <v>1</v>
       </c>
       <c r="C55" t="s">
         <v>42</v>
